--- a/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
+++ b/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
@@ -331,7 +331,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -364,12 +364,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>14</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3273470"/>
+    <ext cx="5905500" cy="3263218"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -435,7 +435,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2846112"/>
+    <ext cx="5905500" cy="3295926"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2194,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO58"/>
+  <dimension ref="A1:AR58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2238,6 +2238,9 @@
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2410,45 +2413,60 @@
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>cesta baixa (R$)</t>
+          <t>consumo baixo (R$)</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>cesta mediana (R$)</t>
+          <t>consumo mediano (R$)</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>cesta alta (R$)</t>
+          <t>consumo alto (R$)</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
+          <t>cesta completa baixa (R$)</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>cesta completa mediana (R$)</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>cesta completa alta (R$)</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
           <t>hambúrguer (R$)</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>batata (R$)</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>cerveja (R$)</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>refrigerante (R$)</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>drinks (R$)</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>títulos no acervo</t>
         </is>
@@ -2564,20 +2582,23 @@
       <c r="AI3" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AJ3" s="14" t="n">
+      <c r="AJ3" s="14" t="n"/>
+      <c r="AK3" s="14" t="n"/>
+      <c r="AL3" s="14" t="n"/>
+      <c r="AM3" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="AK3" s="14" t="n">
+      <c r="AN3" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AL3" s="14" t="n">
+      <c r="AO3" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AM3" s="14" t="n">
+      <c r="AP3" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="AN3" s="14" t="n"/>
-      <c r="AO3" s="15" t="n"/>
+      <c r="AQ3" s="14" t="n"/>
+      <c r="AR3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -2680,7 +2701,10 @@
       <c r="AL4" s="14" t="n"/>
       <c r="AM4" s="14" t="n"/>
       <c r="AN4" s="14" t="n"/>
-      <c r="AO4" s="15" t="n"/>
+      <c r="AO4" s="14" t="n"/>
+      <c r="AP4" s="14" t="n"/>
+      <c r="AQ4" s="14" t="n"/>
+      <c r="AR4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -2794,14 +2818,17 @@
       </c>
       <c r="AJ5" s="14" t="n"/>
       <c r="AK5" s="14" t="n"/>
-      <c r="AL5" s="14" t="n">
+      <c r="AL5" s="14" t="n"/>
+      <c r="AM5" s="14" t="n"/>
+      <c r="AN5" s="14" t="n"/>
+      <c r="AO5" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AM5" s="14" t="n">
+      <c r="AP5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AN5" s="14" t="n"/>
-      <c r="AO5" s="15" t="n"/>
+      <c r="AQ5" s="14" t="n"/>
+      <c r="AR5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -2907,30 +2934,39 @@
         <v>33</v>
       </c>
       <c r="AG6" s="14" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="AH6" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI6" s="14" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="AJ6" s="14" t="n">
         <v>54.5</v>
       </c>
-      <c r="AH6" s="14" t="n">
+      <c r="AK6" s="14" t="n">
         <v>67.5</v>
       </c>
-      <c r="AI6" s="14" t="n">
+      <c r="AL6" s="14" t="n">
         <v>81.5</v>
       </c>
-      <c r="AJ6" s="14" t="n">
+      <c r="AM6" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AK6" s="14" t="n">
+      <c r="AN6" s="14" t="n">
         <v>30.5</v>
       </c>
-      <c r="AL6" s="14" t="n">
+      <c r="AO6" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM6" s="14" t="n">
+      <c r="AP6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AN6" s="14" t="n">
+      <c r="AQ6" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="AO6" s="15" t="n">
+      <c r="AR6" s="15" t="n">
         <v>150</v>
       </c>
     </row>
@@ -3038,26 +3074,35 @@
         <v>31</v>
       </c>
       <c r="AG7" s="14" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AH7" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI7" s="14" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="AJ7" s="14" t="n">
         <v>64.5</v>
       </c>
-      <c r="AH7" s="14" t="n">
+      <c r="AK7" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="AI7" s="14" t="n">
+      <c r="AL7" s="14" t="n">
         <v>76.75</v>
       </c>
-      <c r="AJ7" s="14" t="n"/>
-      <c r="AK7" s="14" t="n"/>
-      <c r="AL7" s="14" t="n">
+      <c r="AM7" s="14" t="n"/>
+      <c r="AN7" s="14" t="n"/>
+      <c r="AO7" s="14" t="n">
         <v>8.5</v>
       </c>
-      <c r="AM7" s="14" t="n">
+      <c r="AP7" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AN7" s="14" t="n">
+      <c r="AQ7" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="AO7" s="15" t="n">
+      <c r="AR7" s="15" t="n">
         <v>952</v>
       </c>
     </row>
@@ -3172,17 +3217,20 @@
         <v>84.5</v>
       </c>
       <c r="AJ8" s="14" t="n"/>
-      <c r="AK8" s="14" t="n">
+      <c r="AK8" s="14" t="n"/>
+      <c r="AL8" s="14" t="n"/>
+      <c r="AM8" s="14" t="n"/>
+      <c r="AN8" s="14" t="n">
         <v>25.5</v>
       </c>
-      <c r="AL8" s="14" t="n">
+      <c r="AO8" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="AM8" s="14" t="n">
+      <c r="AP8" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AN8" s="14" t="n"/>
-      <c r="AO8" s="15" t="n"/>
+      <c r="AQ8" s="14" t="n"/>
+      <c r="AR8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3283,7 +3331,10 @@
       <c r="AL9" s="14" t="n"/>
       <c r="AM9" s="14" t="n"/>
       <c r="AN9" s="14" t="n"/>
-      <c r="AO9" s="15" t="n">
+      <c r="AO9" s="14" t="n"/>
+      <c r="AP9" s="14" t="n"/>
+      <c r="AQ9" s="14" t="n"/>
+      <c r="AR9" s="15" t="n">
         <v>214</v>
       </c>
     </row>
@@ -3397,22 +3448,25 @@
       <c r="AI10" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AJ10" s="14" t="n">
+      <c r="AJ10" s="14" t="n"/>
+      <c r="AK10" s="14" t="n"/>
+      <c r="AL10" s="14" t="n"/>
+      <c r="AM10" s="14" t="n">
         <v>29.5</v>
       </c>
-      <c r="AK10" s="14" t="n">
+      <c r="AN10" s="14" t="n">
         <v>26.5</v>
       </c>
-      <c r="AL10" s="14" t="n">
+      <c r="AO10" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AM10" s="14" t="n">
+      <c r="AP10" s="14" t="n">
         <v>7.5</v>
       </c>
-      <c r="AN10" s="14" t="n">
+      <c r="AQ10" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AO10" s="15" t="n">
+      <c r="AR10" s="15" t="n">
         <v>1833</v>
       </c>
     </row>
@@ -3505,7 +3559,10 @@
       <c r="AL11" s="14" t="n"/>
       <c r="AM11" s="14" t="n"/>
       <c r="AN11" s="14" t="n"/>
-      <c r="AO11" s="15" t="n"/>
+      <c r="AO11" s="14" t="n"/>
+      <c r="AP11" s="14" t="n"/>
+      <c r="AQ11" s="14" t="n"/>
+      <c r="AR11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -3617,18 +3674,21 @@
       <c r="AI12" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="AJ12" s="14" t="n">
+      <c r="AJ12" s="14" t="n"/>
+      <c r="AK12" s="14" t="n"/>
+      <c r="AL12" s="14" t="n"/>
+      <c r="AM12" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="AK12" s="14" t="n">
+      <c r="AN12" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="AL12" s="14" t="n">
+      <c r="AO12" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM12" s="14" t="n"/>
-      <c r="AN12" s="14" t="n"/>
-      <c r="AO12" s="15" t="n">
+      <c r="AP12" s="14" t="n"/>
+      <c r="AQ12" s="14" t="n"/>
+      <c r="AR12" s="15" t="n">
         <v>312</v>
       </c>
     </row>
@@ -3742,22 +3802,25 @@
       <c r="AI13" s="14" t="n">
         <v>60.5</v>
       </c>
-      <c r="AJ13" s="14" t="n">
+      <c r="AJ13" s="14" t="n"/>
+      <c r="AK13" s="14" t="n"/>
+      <c r="AL13" s="14" t="n"/>
+      <c r="AM13" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AK13" s="14" t="n">
+      <c r="AN13" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="AL13" s="14" t="n">
+      <c r="AO13" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM13" s="14" t="n">
+      <c r="AP13" s="14" t="n">
         <v>8.9</v>
       </c>
-      <c r="AN13" s="14" t="n">
+      <c r="AQ13" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AO13" s="15" t="n">
+      <c r="AR13" s="15" t="n">
         <v>370</v>
       </c>
     </row>
@@ -3863,30 +3926,39 @@
         <v>35</v>
       </c>
       <c r="AG14" s="14" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AH14" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI14" s="14" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AJ14" s="14" t="n">
         <v>56.75</v>
       </c>
-      <c r="AH14" s="14" t="n">
+      <c r="AK14" s="14" t="n">
         <v>73.5</v>
       </c>
-      <c r="AI14" s="14" t="n">
+      <c r="AL14" s="14" t="n">
         <v>81.25</v>
       </c>
-      <c r="AJ14" s="14" t="n">
+      <c r="AM14" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="AK14" s="14" t="n">
+      <c r="AN14" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="AL14" s="14" t="n">
+      <c r="AO14" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AM14" s="14" t="n">
+      <c r="AP14" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="AN14" s="14" t="n">
+      <c r="AQ14" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AO14" s="15" t="n">
+      <c r="AR14" s="15" t="n">
         <v>468</v>
       </c>
     </row>
@@ -3996,20 +4068,23 @@
       <c r="AI15" s="14" t="n">
         <v>71.5</v>
       </c>
-      <c r="AJ15" s="14" t="n">
+      <c r="AJ15" s="14" t="n"/>
+      <c r="AK15" s="14" t="n"/>
+      <c r="AL15" s="14" t="n"/>
+      <c r="AM15" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AK15" s="14" t="n"/>
-      <c r="AL15" s="14" t="n">
+      <c r="AN15" s="14" t="n"/>
+      <c r="AO15" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AM15" s="14" t="n">
+      <c r="AP15" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN15" s="14" t="n">
+      <c r="AQ15" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="AO15" s="15" t="n">
+      <c r="AR15" s="15" t="n">
         <v>588</v>
       </c>
     </row>
@@ -4117,26 +4192,35 @@
         <v>50</v>
       </c>
       <c r="AG16" s="14" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AH16" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI16" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ16" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="AH16" s="14" t="n">
+      <c r="AK16" s="14" t="n">
         <v>85.5</v>
       </c>
-      <c r="AI16" s="14" t="n">
+      <c r="AL16" s="14" t="n">
         <v>98.75</v>
       </c>
-      <c r="AJ16" s="14" t="n">
+      <c r="AM16" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="AK16" s="14" t="n"/>
-      <c r="AL16" s="14" t="n">
+      <c r="AN16" s="14" t="n"/>
+      <c r="AO16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM16" s="14" t="n"/>
-      <c r="AN16" s="14" t="n">
+      <c r="AP16" s="14" t="n"/>
+      <c r="AQ16" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AO16" s="15" t="n">
+      <c r="AR16" s="15" t="n">
         <v>190</v>
       </c>
     </row>
@@ -4241,7 +4325,10 @@
       <c r="AL17" s="14" t="n"/>
       <c r="AM17" s="14" t="n"/>
       <c r="AN17" s="14" t="n"/>
-      <c r="AO17" s="15" t="n"/>
+      <c r="AO17" s="14" t="n"/>
+      <c r="AP17" s="14" t="n"/>
+      <c r="AQ17" s="14" t="n"/>
+      <c r="AR17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -4341,30 +4428,39 @@
         <v>35</v>
       </c>
       <c r="AG18" s="14" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AH18" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI18" s="14" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AJ18" s="14" t="n">
         <v>58.5</v>
       </c>
-      <c r="AH18" s="14" t="n">
+      <c r="AK18" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AI18" s="14" t="n">
+      <c r="AL18" s="14" t="n">
         <v>87.5</v>
       </c>
-      <c r="AJ18" s="14" t="n">
+      <c r="AM18" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AK18" s="14" t="n">
+      <c r="AN18" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="AL18" s="14" t="n">
+      <c r="AO18" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM18" s="14" t="n">
+      <c r="AP18" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN18" s="14" t="n">
+      <c r="AQ18" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AO18" s="15" t="n">
+      <c r="AR18" s="15" t="n">
         <v>192</v>
       </c>
     </row>
@@ -4457,7 +4553,10 @@
       <c r="AL19" s="14" t="n"/>
       <c r="AM19" s="14" t="n"/>
       <c r="AN19" s="14" t="n"/>
-      <c r="AO19" s="15" t="n">
+      <c r="AO19" s="14" t="n"/>
+      <c r="AP19" s="14" t="n"/>
+      <c r="AQ19" s="14" t="n"/>
+      <c r="AR19" s="15" t="n">
         <v>362</v>
       </c>
     </row>
@@ -4565,30 +4664,39 @@
         <v>52</v>
       </c>
       <c r="AG20" s="14" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AH20" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI20" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="AJ20" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="AH20" s="14" t="n">
+      <c r="AK20" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="AI20" s="14" t="n">
+      <c r="AL20" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="AJ20" s="14" t="n">
+      <c r="AM20" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="AK20" s="14" t="n">
+      <c r="AN20" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="AL20" s="14" t="n">
+      <c r="AO20" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AM20" s="14" t="n">
+      <c r="AP20" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AN20" s="14" t="n">
+      <c r="AQ20" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AO20" s="15" t="n">
+      <c r="AR20" s="15" t="n">
         <v>836</v>
       </c>
     </row>
@@ -4693,7 +4801,10 @@
       <c r="AL21" s="14" t="n"/>
       <c r="AM21" s="14" t="n"/>
       <c r="AN21" s="14" t="n"/>
-      <c r="AO21" s="15" t="n"/>
+      <c r="AO21" s="14" t="n"/>
+      <c r="AP21" s="14" t="n"/>
+      <c r="AQ21" s="14" t="n"/>
+      <c r="AR21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -4805,20 +4916,23 @@
       <c r="AI22" s="14" t="n">
         <v>54.5</v>
       </c>
-      <c r="AJ22" s="14" t="n">
+      <c r="AJ22" s="14" t="n"/>
+      <c r="AK22" s="14" t="n"/>
+      <c r="AL22" s="14" t="n"/>
+      <c r="AM22" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="AK22" s="14" t="n">
+      <c r="AN22" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="AL22" s="14" t="n">
+      <c r="AO22" s="14" t="n">
         <v>16.5</v>
       </c>
-      <c r="AM22" s="14" t="n">
+      <c r="AP22" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AN22" s="14" t="n"/>
-      <c r="AO22" s="15" t="n">
+      <c r="AQ22" s="14" t="n"/>
+      <c r="AR22" s="15" t="n">
         <v>780</v>
       </c>
     </row>
@@ -4923,7 +5037,10 @@
       <c r="AL23" s="14" t="n"/>
       <c r="AM23" s="14" t="n"/>
       <c r="AN23" s="14" t="n"/>
-      <c r="AO23" s="15" t="n"/>
+      <c r="AO23" s="14" t="n"/>
+      <c r="AP23" s="14" t="n"/>
+      <c r="AQ23" s="14" t="n"/>
+      <c r="AR23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -5026,7 +5143,10 @@
       <c r="AL24" s="14" t="n"/>
       <c r="AM24" s="14" t="n"/>
       <c r="AN24" s="14" t="n"/>
-      <c r="AO24" s="15" t="n"/>
+      <c r="AO24" s="14" t="n"/>
+      <c r="AP24" s="14" t="n"/>
+      <c r="AQ24" s="14" t="n"/>
+      <c r="AR24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -5123,7 +5243,10 @@
       <c r="AL25" s="14" t="n"/>
       <c r="AM25" s="14" t="n"/>
       <c r="AN25" s="14" t="n"/>
-      <c r="AO25" s="15" t="n">
+      <c r="AO25" s="14" t="n"/>
+      <c r="AP25" s="14" t="n"/>
+      <c r="AQ25" s="14" t="n"/>
+      <c r="AR25" s="15" t="n">
         <v>1357</v>
       </c>
     </row>
@@ -5231,30 +5354,39 @@
         <v>45</v>
       </c>
       <c r="AG26" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH26" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="AI26" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="AJ26" s="14" t="n">
         <v>52.25</v>
       </c>
-      <c r="AH26" s="14" t="n">
+      <c r="AK26" s="14" t="n">
         <v>68.5</v>
       </c>
-      <c r="AI26" s="14" t="n">
+      <c r="AL26" s="14" t="n">
         <v>96.75</v>
       </c>
-      <c r="AJ26" s="14" t="n">
+      <c r="AM26" s="14" t="n">
         <v>52.5</v>
       </c>
-      <c r="AK26" s="14" t="n">
+      <c r="AN26" s="14" t="n">
         <v>28.5</v>
       </c>
-      <c r="AL26" s="14" t="n">
+      <c r="AO26" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="AM26" s="14" t="n">
+      <c r="AP26" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN26" s="14" t="n">
+      <c r="AQ26" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AO26" s="15" t="n">
+      <c r="AR26" s="15" t="n">
         <v>540</v>
       </c>
     </row>
@@ -5368,22 +5500,25 @@
       <c r="AI27" s="14" t="n">
         <v>76</v>
       </c>
-      <c r="AJ27" s="14" t="n">
+      <c r="AJ27" s="14" t="n"/>
+      <c r="AK27" s="14" t="n"/>
+      <c r="AL27" s="14" t="n"/>
+      <c r="AM27" s="14" t="n">
         <v>49.5</v>
       </c>
-      <c r="AK27" s="14" t="n">
+      <c r="AN27" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="AL27" s="14" t="n">
+      <c r="AO27" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="AM27" s="14" t="n">
+      <c r="AP27" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN27" s="14" t="n">
+      <c r="AQ27" s="14" t="n">
         <v>36.5</v>
       </c>
-      <c r="AO27" s="15" t="n">
+      <c r="AR27" s="15" t="n">
         <v>934</v>
       </c>
     </row>
@@ -5486,7 +5621,10 @@
       <c r="AL28" s="14" t="n"/>
       <c r="AM28" s="14" t="n"/>
       <c r="AN28" s="14" t="n"/>
-      <c r="AO28" s="15" t="n"/>
+      <c r="AO28" s="14" t="n"/>
+      <c r="AP28" s="14" t="n"/>
+      <c r="AQ28" s="14" t="n"/>
+      <c r="AR28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -5599,15 +5737,18 @@
         <v>78</v>
       </c>
       <c r="AJ29" s="14" t="n"/>
-      <c r="AK29" s="14" t="n">
-        <v>68</v>
-      </c>
+      <c r="AK29" s="14" t="n"/>
       <c r="AL29" s="14" t="n"/>
       <c r="AM29" s="14" t="n"/>
       <c r="AN29" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO29" s="14" t="n"/>
+      <c r="AP29" s="14" t="n"/>
+      <c r="AQ29" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="AO29" s="15" t="n"/>
+      <c r="AR29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -5719,22 +5860,25 @@
       <c r="AI30" s="14" t="n">
         <v>83.55</v>
       </c>
-      <c r="AJ30" s="14" t="n">
+      <c r="AJ30" s="14" t="n"/>
+      <c r="AK30" s="14" t="n"/>
+      <c r="AL30" s="14" t="n"/>
+      <c r="AM30" s="14" t="n">
         <v>43.9</v>
       </c>
-      <c r="AK30" s="14" t="n">
+      <c r="AN30" s="14" t="n">
         <v>39.9</v>
       </c>
-      <c r="AL30" s="14" t="n">
+      <c r="AO30" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AM30" s="14" t="n">
+      <c r="AP30" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AN30" s="14" t="n">
+      <c r="AQ30" s="14" t="n">
         <v>37.9</v>
       </c>
-      <c r="AO30" s="15" t="n">
+      <c r="AR30" s="15" t="n">
         <v>225</v>
       </c>
     </row>
@@ -5848,22 +5992,25 @@
       <c r="AI31" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="AJ31" s="14" t="n">
+      <c r="AJ31" s="14" t="n"/>
+      <c r="AK31" s="14" t="n"/>
+      <c r="AL31" s="14" t="n"/>
+      <c r="AM31" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AK31" s="14" t="n">
+      <c r="AN31" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="AL31" s="14" t="n">
+      <c r="AO31" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="AM31" s="14" t="n">
+      <c r="AP31" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN31" s="14" t="n">
+      <c r="AQ31" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="AO31" s="15" t="n"/>
+      <c r="AR31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -5975,22 +6122,25 @@
       <c r="AI32" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="AJ32" s="14" t="n">
+      <c r="AJ32" s="14" t="n"/>
+      <c r="AK32" s="14" t="n"/>
+      <c r="AL32" s="14" t="n"/>
+      <c r="AM32" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="AK32" s="14" t="n">
+      <c r="AN32" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="AL32" s="14" t="n">
+      <c r="AO32" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="AM32" s="14" t="n">
+      <c r="AP32" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN32" s="14" t="n">
+      <c r="AQ32" s="14" t="n">
         <v>21.5</v>
       </c>
-      <c r="AO32" s="15" t="n">
+      <c r="AR32" s="15" t="n">
         <v>239</v>
       </c>
     </row>
@@ -6104,22 +6254,25 @@
       <c r="AI33" s="14" t="n">
         <v>52.5</v>
       </c>
-      <c r="AJ33" s="14" t="n">
+      <c r="AJ33" s="14" t="n"/>
+      <c r="AK33" s="14" t="n"/>
+      <c r="AL33" s="14" t="n"/>
+      <c r="AM33" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="AK33" s="14" t="n">
+      <c r="AN33" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="AL33" s="14" t="n">
+      <c r="AO33" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM33" s="14" t="n">
+      <c r="AP33" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN33" s="14" t="n">
+      <c r="AQ33" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AO33" s="15" t="n">
+      <c r="AR33" s="15" t="n">
         <v>90</v>
       </c>
     </row>
@@ -6233,16 +6386,19 @@
       <c r="AI34" s="14" t="n">
         <v>76.8</v>
       </c>
-      <c r="AJ34" s="14" t="n">
+      <c r="AJ34" s="14" t="n"/>
+      <c r="AK34" s="14" t="n"/>
+      <c r="AL34" s="14" t="n"/>
+      <c r="AM34" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="AK34" s="14" t="n">
+      <c r="AN34" s="14" t="n">
         <v>24.9</v>
       </c>
-      <c r="AL34" s="14" t="n"/>
-      <c r="AM34" s="14" t="n"/>
-      <c r="AN34" s="14" t="n"/>
-      <c r="AO34" s="15" t="n"/>
+      <c r="AO34" s="14" t="n"/>
+      <c r="AP34" s="14" t="n"/>
+      <c r="AQ34" s="14" t="n"/>
+      <c r="AR34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
@@ -6345,7 +6501,10 @@
       <c r="AL35" s="14" t="n"/>
       <c r="AM35" s="14" t="n"/>
       <c r="AN35" s="14" t="n"/>
-      <c r="AO35" s="15" t="n"/>
+      <c r="AO35" s="14" t="n"/>
+      <c r="AP35" s="14" t="n"/>
+      <c r="AQ35" s="14" t="n"/>
+      <c r="AR35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
@@ -6457,20 +6616,23 @@
       <c r="AI36" s="14" t="n">
         <v>41.9</v>
       </c>
-      <c r="AJ36" s="14" t="n">
+      <c r="AJ36" s="14" t="n"/>
+      <c r="AK36" s="14" t="n"/>
+      <c r="AL36" s="14" t="n"/>
+      <c r="AM36" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AK36" s="14" t="n">
+      <c r="AN36" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="AL36" s="14" t="n">
+      <c r="AO36" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="AM36" s="14" t="n">
+      <c r="AP36" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AN36" s="14" t="n"/>
-      <c r="AO36" s="15" t="n"/>
+      <c r="AQ36" s="14" t="n"/>
+      <c r="AR36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
@@ -6577,11 +6739,14 @@
       <c r="AJ37" s="14" t="n"/>
       <c r="AK37" s="14" t="n"/>
       <c r="AL37" s="14" t="n"/>
-      <c r="AM37" s="14" t="n">
+      <c r="AM37" s="14" t="n"/>
+      <c r="AN37" s="14" t="n"/>
+      <c r="AO37" s="14" t="n"/>
+      <c r="AP37" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AN37" s="14" t="n"/>
-      <c r="AO37" s="15" t="n">
+      <c r="AQ37" s="14" t="n"/>
+      <c r="AR37" s="15" t="n">
         <v>331</v>
       </c>
     </row>
@@ -6696,21 +6861,30 @@
         <v>92.5</v>
       </c>
       <c r="AJ38" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="AK38" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="AL38" s="14" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="AM38" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AK38" s="14" t="n">
+      <c r="AN38" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="AL38" s="14" t="n">
+      <c r="AO38" s="14" t="n">
         <v>18.5</v>
       </c>
-      <c r="AM38" s="14" t="n">
+      <c r="AP38" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AN38" s="14" t="n">
+      <c r="AQ38" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="AO38" s="15" t="n">
+      <c r="AR38" s="15" t="n">
         <v>199</v>
       </c>
     </row>
@@ -6815,7 +6989,10 @@
       <c r="AL39" s="14" t="n"/>
       <c r="AM39" s="14" t="n"/>
       <c r="AN39" s="14" t="n"/>
-      <c r="AO39" s="15" t="n">
+      <c r="AO39" s="14" t="n"/>
+      <c r="AP39" s="14" t="n"/>
+      <c r="AQ39" s="14" t="n"/>
+      <c r="AR39" s="15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -6920,7 +7097,10 @@
       <c r="AL40" s="14" t="n"/>
       <c r="AM40" s="14" t="n"/>
       <c r="AN40" s="14" t="n"/>
-      <c r="AO40" s="15" t="n">
+      <c r="AO40" s="14" t="n"/>
+      <c r="AP40" s="14" t="n"/>
+      <c r="AQ40" s="14" t="n"/>
+      <c r="AR40" s="15" t="n">
         <v>227</v>
       </c>
     </row>
@@ -7034,20 +7214,23 @@
       <c r="AI41" s="14" t="n">
         <v>53.5</v>
       </c>
-      <c r="AJ41" s="14" t="n">
+      <c r="AJ41" s="14" t="n"/>
+      <c r="AK41" s="14" t="n"/>
+      <c r="AL41" s="14" t="n"/>
+      <c r="AM41" s="14" t="n">
         <v>38.9</v>
       </c>
-      <c r="AK41" s="14" t="n">
+      <c r="AN41" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="AL41" s="14" t="n">
+      <c r="AO41" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AM41" s="14" t="n">
+      <c r="AP41" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="AN41" s="14" t="n"/>
-      <c r="AO41" s="15" t="n">
+      <c r="AQ41" s="14" t="n"/>
+      <c r="AR41" s="15" t="n">
         <v>633</v>
       </c>
     </row>
@@ -7162,17 +7345,20 @@
         <v>34.5</v>
       </c>
       <c r="AJ42" s="14" t="n"/>
-      <c r="AK42" s="14" t="n">
+      <c r="AK42" s="14" t="n"/>
+      <c r="AL42" s="14" t="n"/>
+      <c r="AM42" s="14" t="n"/>
+      <c r="AN42" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="AL42" s="14" t="n">
+      <c r="AO42" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="AM42" s="14" t="n">
+      <c r="AP42" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AN42" s="14" t="n"/>
-      <c r="AO42" s="15" t="n">
+      <c r="AQ42" s="14" t="n"/>
+      <c r="AR42" s="15" t="n">
         <v>438</v>
       </c>
     </row>
@@ -7274,16 +7460,19 @@
       <c r="AG43" s="14" t="n"/>
       <c r="AH43" s="14" t="n"/>
       <c r="AI43" s="14" t="n"/>
-      <c r="AJ43" s="14" t="n">
+      <c r="AJ43" s="14" t="n"/>
+      <c r="AK43" s="14" t="n"/>
+      <c r="AL43" s="14" t="n"/>
+      <c r="AM43" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="AK43" s="14" t="n">
+      <c r="AN43" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="AL43" s="14" t="n"/>
-      <c r="AM43" s="14" t="n"/>
-      <c r="AN43" s="14" t="n"/>
-      <c r="AO43" s="15" t="n">
+      <c r="AO43" s="14" t="n"/>
+      <c r="AP43" s="14" t="n"/>
+      <c r="AQ43" s="14" t="n"/>
+      <c r="AR43" s="15" t="n">
         <v>221</v>
       </c>
     </row>
@@ -7388,7 +7577,10 @@
       <c r="AL44" s="14" t="n"/>
       <c r="AM44" s="14" t="n"/>
       <c r="AN44" s="14" t="n"/>
-      <c r="AO44" s="15" t="n"/>
+      <c r="AO44" s="14" t="n"/>
+      <c r="AP44" s="14" t="n"/>
+      <c r="AQ44" s="14" t="n"/>
+      <c r="AR44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
@@ -7499,17 +7691,20 @@
         <v>30.25</v>
       </c>
       <c r="AJ45" s="14" t="n"/>
-      <c r="AK45" s="14" t="n">
+      <c r="AK45" s="14" t="n"/>
+      <c r="AL45" s="14" t="n"/>
+      <c r="AM45" s="14" t="n"/>
+      <c r="AN45" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="AL45" s="14" t="n">
+      <c r="AO45" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AM45" s="14" t="n">
+      <c r="AP45" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="AN45" s="14" t="n"/>
-      <c r="AO45" s="15" t="n"/>
+      <c r="AQ45" s="14" t="n"/>
+      <c r="AR45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
@@ -7622,11 +7817,14 @@
       <c r="AJ46" s="14" t="n"/>
       <c r="AK46" s="14" t="n"/>
       <c r="AL46" s="14" t="n"/>
-      <c r="AM46" s="14" t="n">
+      <c r="AM46" s="14" t="n"/>
+      <c r="AN46" s="14" t="n"/>
+      <c r="AO46" s="14" t="n"/>
+      <c r="AP46" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AN46" s="14" t="n"/>
-      <c r="AO46" s="15" t="n">
+      <c r="AQ46" s="14" t="n"/>
+      <c r="AR46" s="15" t="n">
         <v>270</v>
       </c>
     </row>
@@ -7738,22 +7936,25 @@
       <c r="AI47" s="14" t="n">
         <v>58</v>
       </c>
-      <c r="AJ47" s="14" t="n">
+      <c r="AJ47" s="14" t="n"/>
+      <c r="AK47" s="14" t="n"/>
+      <c r="AL47" s="14" t="n"/>
+      <c r="AM47" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="AK47" s="14" t="n">
+      <c r="AN47" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="AL47" s="14" t="n">
+      <c r="AO47" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="AM47" s="14" t="n">
+      <c r="AP47" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN47" s="14" t="n">
+      <c r="AQ47" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="AO47" s="15" t="n"/>
+      <c r="AR47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
@@ -7854,7 +8055,10 @@
       <c r="AL48" s="14" t="n"/>
       <c r="AM48" s="14" t="n"/>
       <c r="AN48" s="14" t="n"/>
-      <c r="AO48" s="15" t="n">
+      <c r="AO48" s="14" t="n"/>
+      <c r="AP48" s="14" t="n"/>
+      <c r="AQ48" s="14" t="n"/>
+      <c r="AR48" s="15" t="n">
         <v>1010</v>
       </c>
     </row>
@@ -7957,7 +8161,10 @@
       <c r="AL49" s="14" t="n"/>
       <c r="AM49" s="14" t="n"/>
       <c r="AN49" s="14" t="n"/>
-      <c r="AO49" s="15" t="n"/>
+      <c r="AO49" s="14" t="n"/>
+      <c r="AP49" s="14" t="n"/>
+      <c r="AQ49" s="14" t="n"/>
+      <c r="AR49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
@@ -8058,7 +8265,10 @@
       <c r="AL50" s="14" t="n"/>
       <c r="AM50" s="14" t="n"/>
       <c r="AN50" s="14" t="n"/>
-      <c r="AO50" s="15" t="n"/>
+      <c r="AO50" s="14" t="n"/>
+      <c r="AP50" s="14" t="n"/>
+      <c r="AQ50" s="14" t="n"/>
+      <c r="AR50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
@@ -8159,7 +8369,10 @@
       <c r="AL51" s="14" t="n"/>
       <c r="AM51" s="14" t="n"/>
       <c r="AN51" s="14" t="n"/>
-      <c r="AO51" s="15" t="n"/>
+      <c r="AO51" s="14" t="n"/>
+      <c r="AP51" s="14" t="n"/>
+      <c r="AQ51" s="14" t="n"/>
+      <c r="AR51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -8261,16 +8474,19 @@
       <c r="AG52" s="14" t="n"/>
       <c r="AH52" s="14" t="n"/>
       <c r="AI52" s="14" t="n"/>
-      <c r="AJ52" s="14" t="n">
+      <c r="AJ52" s="14" t="n"/>
+      <c r="AK52" s="14" t="n"/>
+      <c r="AL52" s="14" t="n"/>
+      <c r="AM52" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="AK52" s="14" t="n">
+      <c r="AN52" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="AL52" s="14" t="n"/>
-      <c r="AM52" s="14" t="n"/>
-      <c r="AN52" s="14" t="n"/>
-      <c r="AO52" s="15" t="n"/>
+      <c r="AO52" s="14" t="n"/>
+      <c r="AP52" s="14" t="n"/>
+      <c r="AQ52" s="14" t="n"/>
+      <c r="AR52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
@@ -8376,16 +8592,19 @@
       <c r="AI53" s="14" t="n">
         <v>37.6</v>
       </c>
-      <c r="AJ53" s="14" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="AJ53" s="14" t="n"/>
       <c r="AK53" s="14" t="n"/>
       <c r="AL53" s="14" t="n"/>
       <c r="AM53" s="14" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AN53" s="14" t="n"/>
+      <c r="AO53" s="14" t="n"/>
+      <c r="AP53" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="AN53" s="14" t="n"/>
-      <c r="AO53" s="15" t="n">
+      <c r="AQ53" s="14" t="n"/>
+      <c r="AR53" s="15" t="n">
         <v>245</v>
       </c>
     </row>
@@ -8497,22 +8716,25 @@
       <c r="AI54" s="14" t="n">
         <v>67.67</v>
       </c>
-      <c r="AJ54" s="14" t="n">
+      <c r="AJ54" s="14" t="n"/>
+      <c r="AK54" s="14" t="n"/>
+      <c r="AL54" s="14" t="n"/>
+      <c r="AM54" s="14" t="n">
         <v>29.9</v>
       </c>
-      <c r="AK54" s="14" t="n">
+      <c r="AN54" s="14" t="n">
         <v>29.2</v>
       </c>
-      <c r="AL54" s="14" t="n">
+      <c r="AO54" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="AM54" s="14" t="n">
+      <c r="AP54" s="14" t="n">
         <v>6.75</v>
       </c>
-      <c r="AN54" s="14" t="n">
+      <c r="AQ54" s="14" t="n">
         <v>20.9</v>
       </c>
-      <c r="AO54" s="15" t="n"/>
+      <c r="AR54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
@@ -8624,22 +8846,25 @@
       <c r="AI55" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="AJ55" s="14" t="n">
+      <c r="AJ55" s="14" t="n"/>
+      <c r="AK55" s="14" t="n"/>
+      <c r="AL55" s="14" t="n"/>
+      <c r="AM55" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AK55" s="14" t="n">
+      <c r="AN55" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AL55" s="14" t="n">
+      <c r="AO55" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="AM55" s="14" t="n">
+      <c r="AP55" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AN55" s="14" t="n">
+      <c r="AQ55" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="AO55" s="15" t="n"/>
+      <c r="AR55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -8748,11 +8973,14 @@
       <c r="AJ56" s="18" t="n"/>
       <c r="AK56" s="18" t="n"/>
       <c r="AL56" s="18" t="n"/>
-      <c r="AM56" s="18" t="n">
+      <c r="AM56" s="18" t="n"/>
+      <c r="AN56" s="18" t="n"/>
+      <c r="AO56" s="18" t="n"/>
+      <c r="AP56" s="18" t="n">
         <v>7.5</v>
       </c>
-      <c r="AN56" s="18" t="n"/>
-      <c r="AO56" s="19" t="n">
+      <c r="AQ56" s="18" t="n"/>
+      <c r="AR56" s="19" t="n">
         <v>287</v>
       </c>
     </row>
@@ -8772,7 +9000,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A1:AR1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9140,7 +9368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10188,7 +10416,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível baixo (R$)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível baixo (R$)</t>
         </is>
       </c>
       <c r="C23" s="4">
@@ -10236,7 +10464,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível mediano (R$)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível mediano (R$)</t>
         </is>
       </c>
       <c r="C24" s="4">
@@ -10284,7 +10512,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível alto (R$)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível alto (R$)</t>
         </is>
       </c>
       <c r="C25" s="4">
@@ -10325,69 +10553,213 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Cardápio</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Cesta completa (consumo + couvert encontrado), nível baixo (R$)</t>
+        </is>
+      </c>
+      <c r="C26" s="4">
+        <f>COUNT('Dados B1'!$AJ$3:$AJ$56)</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>ROWS('Dados B1'!$AJ$3:$AJ$56)-COUNT('Dados B1'!$AJ$3:$AJ$56)</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>IFERROR(AVERAGE('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>IFERROR(MEDIAN('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>IFERROR(STDEV('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>IFERROR(MIN('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AJ$3:$AJ$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AJ$3:$AJ$56,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="10">
+        <f>IFERROR(MAX('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Cardápio</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Cesta completa (consumo + couvert encontrado), nível mediano (R$)</t>
+        </is>
+      </c>
+      <c r="C27" s="4">
+        <f>COUNT('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>ROWS('Dados B1'!$AK$3:$AK$56)-COUNT('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
+      <c r="E27" s="10">
+        <f>IFERROR(AVERAGE('Dados B1'!$AK$3:$AK$56),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="10">
+        <f>IFERROR(MEDIAN('Dados B1'!$AK$3:$AK$56),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="10">
+        <f>IFERROR(STDEV('Dados B1'!$AK$3:$AK$56),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="10">
+        <f>IFERROR(MIN('Dados B1'!$AK$3:$AK$56),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AK$3:$AK$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AK$3:$AK$56,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="10">
+        <f>IFERROR(MAX('Dados B1'!$AK$3:$AK$56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Cardápio</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Cesta completa (consumo + couvert encontrado), nível alto (R$)</t>
+        </is>
+      </c>
+      <c r="C28" s="4">
+        <f>COUNT('Dados B1'!$AL$3:$AL$56)</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f>ROWS('Dados B1'!$AL$3:$AL$56)-COUNT('Dados B1'!$AL$3:$AL$56)</f>
+        <v/>
+      </c>
+      <c r="E28" s="10">
+        <f>IFERROR(AVERAGE('Dados B1'!$AL$3:$AL$56),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>IFERROR(MEDIAN('Dados B1'!$AL$3:$AL$56),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="10">
+        <f>IFERROR(STDEV('Dados B1'!$AL$3:$AL$56),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="10">
+        <f>IFERROR(MIN('Dados B1'!$AL$3:$AL$56),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AL$3:$AL$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AL$3:$AL$56,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="10">
+        <f>IFERROR(MAX('Dados B1'!$AL$3:$AL$56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Acervo</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Títulos no acervo publicado</t>
         </is>
       </c>
-      <c r="C26" s="7">
-        <f>COUNT('Dados B1'!$AO$3:$AO$56)</f>
-        <v/>
-      </c>
-      <c r="D26" s="7">
-        <f>ROWS('Dados B1'!$AO$3:$AO$56)-COUNT('Dados B1'!$AO$3:$AO$56)</f>
-        <v/>
-      </c>
-      <c r="E26" s="11">
-        <f>IFERROR(AVERAGE('Dados B1'!$AO$3:$AO$56),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="11">
-        <f>IFERROR(MEDIAN('Dados B1'!$AO$3:$AO$56),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="11">
-        <f>IFERROR(STDEV('Dados B1'!$AO$3:$AO$56),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="11">
-        <f>IFERROR(MIN('Dados B1'!$AO$3:$AO$56),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="11">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AO$3:$AO$56,0.25),"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="11">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AO$3:$AO$56,0.75),"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="11">
-        <f>IFERROR(MAX('Dados B1'!$AO$3:$AO$56),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="C29" s="7">
+        <f>COUNT('Dados B1'!$AR$3:$AR$56)</f>
+        <v/>
+      </c>
+      <c r="D29" s="7">
+        <f>ROWS('Dados B1'!$AR$3:$AR$56)-COUNT('Dados B1'!$AR$3:$AR$56)</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>IFERROR(AVERAGE('Dados B1'!$AR$3:$AR$56),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
+        <f>IFERROR(MEDIAN('Dados B1'!$AR$3:$AR$56),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IFERROR(STDEV('Dados B1'!$AR$3:$AR$56),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="11">
+        <f>IFERROR(MIN('Dados B1'!$AR$3:$AR$56),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="11">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AR$3:$AR$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="11">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AR$3:$AR$56,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="11">
+        <f>IFERROR(MAX('Dados B1'!$AR$3:$AR$56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Fonte: B1, Google Places API (09/2026 e 15/10/2026), coletor de entorno do Google Maps (15/10/2026), Instagram (01/09 a 01/10/2026) e cardápios</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Nota: desvio padrão amostral; quartis pelo método inclusivo. Engajamento em fração (0,01 = 1%).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Entorno sem OpenStreetMap: shoppings de porte fora. Distância ao metrô vazia onde a cidade não tem metrô lido (Curitiba, Florianópolis, Belém, Goiânia, Vitória).</t>
         </is>
@@ -10607,7 +10979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10620,6 +10992,8 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10672,12 +11046,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>casas com cesta</t>
+          <t>casas com consumo</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>cesta mediana (mediana, R$)</t>
+          <t>consumo mediano (mediana, R$)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>casas com cesta completa</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>cesta completa mediana (mediana, R$)</t>
         </is>
       </c>
     </row>
@@ -10723,6 +11107,14 @@
         <f t="array" ref="J3">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A3,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="K3" s="4">
+        <f>COUNTIFS('Dados B1'!$C$3:$C$56,$A3,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="L3" s="10">
+        <f t="array" ref="L3">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A3,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -10766,6 +11158,14 @@
         <f t="array" ref="J4">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A4,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="K4" s="4">
+        <f>COUNTIFS('Dados B1'!$C$3:$C$56,$A4,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="L4" s="10">
+        <f t="array" ref="L4">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A4,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -10809,6 +11209,14 @@
         <f t="array" ref="J5">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A5,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="K5" s="4">
+        <f>COUNTIFS('Dados B1'!$C$3:$C$56,$A5,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="L5" s="10">
+        <f t="array" ref="L5">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A5,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -10852,6 +11260,14 @@
         <f t="array" ref="J6">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A6,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="K6" s="4">
+        <f>COUNTIFS('Dados B1'!$C$3:$C$56,$A6,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="L6" s="10">
+        <f t="array" ref="L6">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A6,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -10895,6 +11311,14 @@
         <f t="array" ref="J7">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A7,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="K7" s="4">
+        <f>COUNTIFS('Dados B1'!$C$3:$C$56,$A7,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="L7" s="10">
+        <f t="array" ref="L7">IFERROR(MEDIAN(IF('Dados B1'!$C$3:$C$56=$A7,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -10938,6 +11362,14 @@
         <f>MEDIAN('Dados B1'!$AH$3:$AH$56)</f>
         <v/>
       </c>
+      <c r="K8" s="7">
+        <f>COUNT('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
+      <c r="L8" s="11">
+        <f>MEDIAN('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -10949,13 +11381,13 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Nota: medianas calculadas só entre as casas com dado; cesta só nas casas com couvert, bebida e prato encontrados.</t>
+          <t>Nota: medianas calculadas só entre as casas com dado. Consumo = bebida + entrada ou prato, nas casas com os dois no cardápio; cesta completa = consumo + couvert, só nas casas com couvert encontrado (couvert não encontrado não entra como 0).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -10968,7 +11400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10982,6 +11414,8 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11039,12 +11473,22 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>casas com cesta</t>
+          <t>casas com consumo</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>cesta mediana (mediana, R$)</t>
+          <t>consumo mediano (mediana, R$)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>casas com cesta completa</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>cesta completa mediana (mediana, R$)</t>
         </is>
       </c>
     </row>
@@ -11095,6 +11539,14 @@
         <f t="array" ref="K3">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A3,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L3" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A3,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M3" s="10">
+        <f t="array" ref="M3">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A3,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -11143,6 +11595,14 @@
         <f t="array" ref="K4">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A4,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L4" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A4,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M4" s="10">
+        <f t="array" ref="M4">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A4,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11191,6 +11651,14 @@
         <f t="array" ref="K5">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A5,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L5" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A5,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M5" s="10">
+        <f t="array" ref="M5">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A5,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -11239,6 +11707,14 @@
         <f t="array" ref="K6">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A6,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L6" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A6,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M6" s="10">
+        <f t="array" ref="M6">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A6,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -11287,6 +11763,14 @@
         <f t="array" ref="K7">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A7,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L7" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A7,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M7" s="10">
+        <f t="array" ref="M7">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A7,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -11335,6 +11819,14 @@
         <f t="array" ref="K8">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A8,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L8" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A8,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M8" s="10">
+        <f t="array" ref="M8">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A8,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11383,6 +11875,14 @@
         <f t="array" ref="K9">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A9,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L9" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A9,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M9" s="10">
+        <f t="array" ref="M9">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A9,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -11431,6 +11931,14 @@
         <f t="array" ref="K10">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A10,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L10" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A10,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M10" s="10">
+        <f t="array" ref="M10">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A10,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -11479,6 +11987,14 @@
         <f t="array" ref="K11">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A11,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L11" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A11,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M11" s="10">
+        <f t="array" ref="M11">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A11,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -11527,6 +12043,14 @@
         <f t="array" ref="K12">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A12,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L12" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A12,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M12" s="10">
+        <f t="array" ref="M12">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A12,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -11575,6 +12099,14 @@
         <f t="array" ref="K13">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A13,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L13" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A13,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M13" s="10">
+        <f t="array" ref="M13">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A13,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -11623,6 +12155,14 @@
         <f t="array" ref="K14">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A14,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
         <v/>
       </c>
+      <c r="L14" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A14,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M14" s="10">
+        <f t="array" ref="M14">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A14,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -11669,6 +12209,14 @@
       </c>
       <c r="K15" s="10">
         <f t="array" ref="K15">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A15,IF('Dados B1'!$AH$3:$AH$56&lt;&gt;"",'Dados B1'!$AH$3:$AH$56))),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>COUNTIFS('Dados B1'!$B$3:$B$56,$A15,'Dados B1'!$AK$3:$AK$56,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="M15" s="10">
+        <f t="array" ref="M15">IFERROR(MEDIAN(IF('Dados B1'!$B$3:$B$56=$A15,IF('Dados B1'!$AK$3:$AK$56&lt;&gt;"",'Dados B1'!$AK$3:$AK$56))),"")</f>
         <v/>
       </c>
     </row>
@@ -11715,6 +12263,14 @@
         <f>MEDIAN('Dados B1'!$AH$3:$AH$56)</f>
         <v/>
       </c>
+      <c r="L16" s="7">
+        <f>COUNT('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11">
+        <f>MEDIAN('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -11726,13 +12282,20 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Nota: o gráfico mostra a mediana da cesta mediana das casas com cesta em cada metrópole; metrópoles sem cesta ficam fora.</t>
+          <t>Nota: o gráfico mostra a mediana do consumo mediano das casas com consumo em cada metrópole; metrópoles sem consumo ficam fora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Consumo = bebida + entrada ou prato, nas casas com os dois no cardápio; cesta completa = consumo + couvert, só nas casas com couvert encontrado (couvert não encontrado não entra como 0).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -11973,7 +12536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -12093,19 +12656,19 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNT('Dados B1'!$AJ$3:$AJ$56)</f>
+        <f>COUNT('Dados B1'!$AM$3:$AM$56)</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AJ$3:$AJ$56,0.25),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AM$3:$AM$56,0.25),"")</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>IFERROR(MEDIAN('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <f>IFERROR(MEDIAN('Dados B1'!$AM$3:$AM$56),"")</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AJ$3:$AJ$56,0.75),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AM$3:$AM$56,0.75),"")</f>
         <v/>
       </c>
     </row>
@@ -12116,19 +12679,19 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNT('Dados B1'!$AK$3:$AK$56)</f>
+        <f>COUNT('Dados B1'!$AN$3:$AN$56)</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AK$3:$AK$56,0.25),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AN$3:$AN$56,0.25),"")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(MEDIAN('Dados B1'!$AK$3:$AK$56),"")</f>
+        <f>IFERROR(MEDIAN('Dados B1'!$AN$3:$AN$56),"")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AK$3:$AK$56,0.75),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AN$3:$AN$56,0.75),"")</f>
         <v/>
       </c>
     </row>
@@ -12139,19 +12702,19 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNT('Dados B1'!$AL$3:$AL$56)</f>
+        <f>COUNT('Dados B1'!$AO$3:$AO$56)</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AL$3:$AL$56,0.25),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AO$3:$AO$56,0.25),"")</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(MEDIAN('Dados B1'!$AL$3:$AL$56),"")</f>
+        <f>IFERROR(MEDIAN('Dados B1'!$AO$3:$AO$56),"")</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AL$3:$AL$56,0.75),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AO$3:$AO$56,0.75),"")</f>
         <v/>
       </c>
     </row>
@@ -12162,19 +12725,19 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNT('Dados B1'!$AM$3:$AM$56)</f>
+        <f>COUNT('Dados B1'!$AP$3:$AP$56)</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AM$3:$AM$56,0.25),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AP$3:$AP$56,0.25),"")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(MEDIAN('Dados B1'!$AM$3:$AM$56),"")</f>
+        <f>IFERROR(MEDIAN('Dados B1'!$AP$3:$AP$56),"")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AM$3:$AM$56,0.75),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AP$3:$AP$56,0.75),"")</f>
         <v/>
       </c>
     </row>
@@ -12185,26 +12748,26 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <f>COUNT('Dados B1'!$AN$3:$AN$56)</f>
+        <f>COUNT('Dados B1'!$AQ$3:$AQ$56)</f>
         <v/>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AN$3:$AN$56,0.25),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AQ$3:$AQ$56,0.25),"")</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(MEDIAN('Dados B1'!$AN$3:$AN$56),"")</f>
+        <f>IFERROR(MEDIAN('Dados B1'!$AQ$3:$AQ$56),"")</f>
         <v/>
       </c>
       <c r="E10" s="10">
-        <f>IFERROR(PERCENTILE('Dados B1'!$AN$3:$AN$56,0.75),"")</f>
+        <f>IFERROR(PERCENTILE('Dados B1'!$AQ$3:$AQ$56,0.75),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível baixo</t>
+          <t>Consumo por pessoa, nível baixo</t>
         </is>
       </c>
       <c r="B11" s="4">
@@ -12227,7 +12790,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível mediano</t>
+          <t>Consumo por pessoa, nível mediano</t>
         </is>
       </c>
       <c r="B12" s="4">
@@ -12248,46 +12811,115 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Cesta por pessoa, nível alto</t>
-        </is>
-      </c>
-      <c r="B13" s="7">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Consumo por pessoa, nível alto</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
         <f>COUNT('Dados B1'!$AI$3:$AI$56)</f>
         <v/>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f>IFERROR(PERCENTILE('Dados B1'!$AI$3:$AI$56,0.25),"")</f>
         <v/>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f>IFERROR(MEDIAN('Dados B1'!$AI$3:$AI$56),"")</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <f>IFERROR(PERCENTILE('Dados B1'!$AI$3:$AI$56,0.75),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Cesta completa, nível baixo</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <f>COUNT('Dados B1'!$AJ$3:$AJ$56)</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AJ$3:$AJ$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="10">
+        <f>IFERROR(MEDIAN('Dados B1'!$AJ$3:$AJ$56),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AJ$3:$AJ$56,0.75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Cesta completa, nível mediano</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>COUNT('Dados B1'!$AK$3:$AK$56)</f>
+        <v/>
+      </c>
+      <c r="C15" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AK$3:$AK$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="10">
+        <f>IFERROR(MEDIAN('Dados B1'!$AK$3:$AK$56),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="10">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AK$3:$AK$56,0.75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Cesta completa, nível alto</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>COUNT('Dados B1'!$AL$3:$AL$56)</f>
+        <v/>
+      </c>
+      <c r="C16" s="11">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AL$3:$AL$56,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="11">
+        <f>IFERROR(MEDIAN('Dados B1'!$AL$3:$AL$56),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="11">
+        <f>IFERROR(PERCENTILE('Dados B1'!$AL$3:$AL$56,0.75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Fonte: B1, cardápios transcritos (B1_cardapios_itens_precos.xlsx)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Nota: cada casa entra com a mediana do próprio cardápio na categoria; quartis entre as casas.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Cesta = couvert + bebida + entrada ou prato, só nas casas em que os três foram encontrados.</t>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Consumo = bebida + entrada ou prato, nas casas com os dois no cardápio; cesta completa = consumo + couvert, só nas casas com couvert encontrado (couvert não encontrado não entra como 0).</t>
         </is>
       </c>
     </row>

--- a/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
+++ b/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 8" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 9" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados B1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Índice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tab 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tab 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tab 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tab 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tab 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tab 6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Tab 7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tab 8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tab 9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Tab 10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Dados B1" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -262,7 +262,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -270,21 +270,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3469613"/>
+    <ext cx="5905500" cy="3395274"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -295,7 +295,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -303,21 +303,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3121190"/>
+    <ext cx="5905500" cy="3111469"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -328,7 +328,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>13</col>
@@ -336,21 +336,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3602946"/>
+    <ext cx="5905500" cy="3540146"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -361,7 +361,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -369,21 +369,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3263218"/>
+    <ext cx="5905500" cy="3188403"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -394,7 +394,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -402,21 +402,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2120488"/>
+    <ext cx="5905500" cy="1955047"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -435,21 +435,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3295926"/>
+    <ext cx="5905500" cy="3183595"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -460,7 +460,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -468,21 +468,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2032566"/>
+    <ext cx="5905500" cy="2008954"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -493,7 +493,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -501,21 +501,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="4366955"/>
+    <ext cx="5905500" cy="4191502"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -526,7 +526,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -534,21 +534,21 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="4481896"/>
+    <ext cx="5905500" cy="4346543"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2661,9 +2661,7 @@
       <c r="R4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="15" t="n">
-        <v>3099</v>
-      </c>
+      <c r="S4" s="15" t="n"/>
       <c r="T4" s="15" t="n">
         <v>76</v>
       </c>
@@ -2770,9 +2768,7 @@
       <c r="S5" s="15" t="n">
         <v>702</v>
       </c>
-      <c r="T5" s="15" t="n">
-        <v>1505</v>
-      </c>
+      <c r="T5" s="15" t="n"/>
       <c r="U5" s="15" t="n">
         <v>6058</v>
       </c>
@@ -3167,9 +3163,7 @@
       <c r="R8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="15" t="n">
-        <v>6361</v>
-      </c>
+      <c r="S8" s="15" t="n"/>
       <c r="T8" s="15" t="n">
         <v>162</v>
       </c>
@@ -3399,9 +3393,7 @@
       <c r="R10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="15" t="n">
-        <v>3702</v>
-      </c>
+      <c r="S10" s="15" t="n"/>
       <c r="T10" s="15" t="n">
         <v>228</v>
       </c>
@@ -3625,12 +3617,8 @@
       <c r="R12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="15" t="n">
-        <v>5144</v>
-      </c>
-      <c r="T12" s="15" t="n">
-        <v>1138</v>
-      </c>
+      <c r="S12" s="15" t="n"/>
+      <c r="T12" s="15" t="n"/>
       <c r="U12" s="15" t="n">
         <v>27673</v>
       </c>
@@ -3908,7 +3896,7 @@
         <v>0.01614</v>
       </c>
       <c r="AA14" s="15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AB14" s="15" t="n">
         <v>1</v>
@@ -3926,7 +3914,7 @@
         <v>35</v>
       </c>
       <c r="AG14" s="14" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="AH14" s="14" t="n">
         <v>48</v>
@@ -3935,7 +3923,7 @@
         <v>54.5</v>
       </c>
       <c r="AJ14" s="14" t="n">
-        <v>56.75</v>
+        <v>54.25</v>
       </c>
       <c r="AK14" s="14" t="n">
         <v>73.5</v>
@@ -3947,7 +3935,7 @@
         <v>40</v>
       </c>
       <c r="AN14" s="14" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="AO14" s="14" t="n">
         <v>13</v>
@@ -4149,9 +4137,7 @@
       <c r="R16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="15" t="n">
-        <v>1142</v>
-      </c>
+      <c r="S16" s="15" t="n"/>
       <c r="T16" s="15" t="n">
         <v>105</v>
       </c>
@@ -4285,9 +4271,7 @@
       <c r="R17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="15" t="n">
-        <v>1201</v>
-      </c>
+      <c r="S17" s="15" t="n"/>
       <c r="T17" s="15" t="n">
         <v>754</v>
       </c>
@@ -4309,12 +4293,18 @@
       <c r="Z17" s="16" t="n">
         <v>0.00134</v>
       </c>
-      <c r="AA17" s="15" t="n"/>
+      <c r="AA17" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="AB17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="15" t="n"/>
-      <c r="AD17" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="AE17" s="14" t="n"/>
       <c r="AF17" s="14" t="n"/>
       <c r="AG17" s="14" t="n"/>
@@ -4391,9 +4381,7 @@
       <c r="R18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="15" t="n">
-        <v>4984</v>
-      </c>
+      <c r="S18" s="15" t="n"/>
       <c r="T18" s="15" t="n">
         <v>137</v>
       </c>
@@ -4525,9 +4513,7 @@
       <c r="R19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="15" t="n">
-        <v>3205</v>
-      </c>
+      <c r="S19" s="15" t="n"/>
       <c r="T19" s="15" t="n">
         <v>391</v>
       </c>
@@ -4537,25 +4523,49 @@
       <c r="X19" s="15" t="n"/>
       <c r="Y19" s="14" t="n"/>
       <c r="Z19" s="16" t="n"/>
-      <c r="AA19" s="15" t="n"/>
+      <c r="AA19" s="15" t="n">
+        <v>11</v>
+      </c>
       <c r="AB19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="15" t="n"/>
-      <c r="AD19" s="14" t="n"/>
-      <c r="AE19" s="14" t="n"/>
-      <c r="AF19" s="14" t="n"/>
-      <c r="AG19" s="14" t="n"/>
-      <c r="AH19" s="14" t="n"/>
-      <c r="AI19" s="14" t="n"/>
-      <c r="AJ19" s="14" t="n"/>
-      <c r="AK19" s="14" t="n"/>
-      <c r="AL19" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AE19" s="14" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AF19" s="14" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AG19" s="14" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AH19" s="14" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AI19" s="14" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AJ19" s="14" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="AK19" s="14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AL19" s="14" t="n">
+        <v>102.05</v>
+      </c>
       <c r="AM19" s="14" t="n"/>
       <c r="AN19" s="14" t="n"/>
       <c r="AO19" s="14" t="n"/>
       <c r="AP19" s="14" t="n"/>
-      <c r="AQ19" s="14" t="n"/>
+      <c r="AQ19" s="14" t="n">
+        <v>38.9</v>
+      </c>
       <c r="AR19" s="15" t="n">
         <v>362</v>
       </c>
@@ -4621,9 +4631,7 @@
       <c r="R20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="15" t="n">
-        <v>2556</v>
-      </c>
+      <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n">
         <v>221</v>
       </c>
@@ -4785,12 +4793,18 @@
       <c r="Z21" s="16" t="n">
         <v>0.00223</v>
       </c>
-      <c r="AA21" s="15" t="n"/>
+      <c r="AA21" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="AB21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="15" t="n"/>
-      <c r="AD21" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="AE21" s="14" t="n"/>
       <c r="AF21" s="14" t="n"/>
       <c r="AG21" s="14" t="n"/>
@@ -4997,9 +5011,7 @@
       <c r="R23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="15" t="n">
-        <v>1216</v>
-      </c>
+      <c r="S23" s="15" t="n"/>
       <c r="T23" s="15" t="n">
         <v>312</v>
       </c>
@@ -5209,9 +5221,7 @@
       <c r="R25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="15" t="n">
-        <v>7638</v>
-      </c>
+      <c r="S25" s="15" t="n"/>
       <c r="T25" s="15" t="n">
         <v>153</v>
       </c>
@@ -5227,25 +5237,49 @@
         <v>207.62</v>
       </c>
       <c r="Z25" s="16" t="n"/>
-      <c r="AA25" s="15" t="n"/>
+      <c r="AA25" s="15" t="n">
+        <v>75</v>
+      </c>
       <c r="AB25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="15" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC25" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="AD25" s="14" t="n"/>
-      <c r="AE25" s="14" t="n"/>
-      <c r="AF25" s="14" t="n"/>
-      <c r="AG25" s="14" t="n"/>
-      <c r="AH25" s="14" t="n"/>
-      <c r="AI25" s="14" t="n"/>
+      <c r="AE25" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF25" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG25" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="AH25" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AI25" s="14" t="n">
+        <v>75.75</v>
+      </c>
       <c r="AJ25" s="14" t="n"/>
       <c r="AK25" s="14" t="n"/>
       <c r="AL25" s="14" t="n"/>
-      <c r="AM25" s="14" t="n"/>
-      <c r="AN25" s="14" t="n"/>
-      <c r="AO25" s="14" t="n"/>
-      <c r="AP25" s="14" t="n"/>
-      <c r="AQ25" s="14" t="n"/>
+      <c r="AM25" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="AN25" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO25" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP25" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ25" s="14" t="n">
+        <v>32</v>
+      </c>
       <c r="AR25" s="15" t="n">
         <v>1357</v>
       </c>
@@ -5314,9 +5348,7 @@
       <c r="S26" s="15" t="n">
         <v>351</v>
       </c>
-      <c r="T26" s="15" t="n">
-        <v>1796</v>
-      </c>
+      <c r="T26" s="15" t="n"/>
       <c r="U26" s="15" t="n">
         <v>6682</v>
       </c>
@@ -5336,7 +5368,7 @@
         <v>0.00353</v>
       </c>
       <c r="AA26" s="15" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AB26" s="15" t="n">
         <v>1</v>
@@ -5351,28 +5383,28 @@
         <v>11</v>
       </c>
       <c r="AF26" s="14" t="n">
-        <v>45</v>
+        <v>39.5</v>
       </c>
       <c r="AG26" s="14" t="n">
-        <v>46</v>
+        <v>43.25</v>
       </c>
       <c r="AH26" s="14" t="n">
-        <v>56</v>
+        <v>50.5</v>
       </c>
       <c r="AI26" s="14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AJ26" s="14" t="n">
-        <v>52.25</v>
+        <v>49.5</v>
       </c>
       <c r="AK26" s="14" t="n">
-        <v>68.5</v>
+        <v>63</v>
       </c>
       <c r="AL26" s="14" t="n">
-        <v>96.75</v>
+        <v>83.75</v>
       </c>
       <c r="AM26" s="14" t="n">
-        <v>52.5</v>
+        <v>42</v>
       </c>
       <c r="AN26" s="14" t="n">
         <v>28.5</v>
@@ -5476,7 +5508,7 @@
         <v>0.00153</v>
       </c>
       <c r="AA27" s="15" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB27" s="15" t="n">
         <v>1</v>
@@ -5498,7 +5530,7 @@
         <v>60</v>
       </c>
       <c r="AI27" s="14" t="n">
-        <v>76</v>
+        <v>77.5</v>
       </c>
       <c r="AJ27" s="14" t="n"/>
       <c r="AK27" s="14" t="n"/>
@@ -5510,7 +5542,7 @@
         <v>39</v>
       </c>
       <c r="AO27" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP27" s="14" t="n">
         <v>8</v>
@@ -5583,9 +5615,7 @@
       <c r="R28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="15" t="n">
-        <v>10228</v>
-      </c>
+      <c r="S28" s="15" t="n"/>
       <c r="T28" s="15" t="n">
         <v>684</v>
       </c>
@@ -5814,9 +5844,7 @@
       <c r="S30" s="15" t="n">
         <v>577</v>
       </c>
-      <c r="T30" s="15" t="n">
-        <v>1006</v>
-      </c>
+      <c r="T30" s="15" t="n"/>
       <c r="U30" s="15" t="n">
         <v>41545</v>
       </c>
@@ -5836,7 +5864,7 @@
         <v>0.00048</v>
       </c>
       <c r="AA30" s="15" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AB30" s="15" t="n">
         <v>1</v>
@@ -5846,16 +5874,16 @@
       </c>
       <c r="AD30" s="14" t="n"/>
       <c r="AE30" s="14" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
       <c r="AF30" s="14" t="n">
         <v>43.4</v>
       </c>
       <c r="AG30" s="14" t="n">
-        <v>55.57</v>
+        <v>54.15</v>
       </c>
       <c r="AH30" s="14" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="AI30" s="14" t="n">
         <v>83.55</v>
@@ -5876,7 +5904,7 @@
         <v>9</v>
       </c>
       <c r="AQ30" s="14" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="AR30" s="15" t="n">
         <v>225</v>
@@ -5968,7 +5996,7 @@
         <v>0.00419</v>
       </c>
       <c r="AA31" s="15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB31" s="15" t="n">
         <v>1</v>
@@ -5984,7 +6012,7 @@
         <v>32</v>
       </c>
       <c r="AG31" s="14" t="n">
-        <v>47.75</v>
+        <v>47.5</v>
       </c>
       <c r="AH31" s="14" t="n">
         <v>60</v>
@@ -5999,7 +6027,7 @@
         <v>28</v>
       </c>
       <c r="AN31" s="14" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AO31" s="14" t="n">
         <v>22</v>
@@ -6073,9 +6101,7 @@
       <c r="R32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="15" t="n">
-        <v>7180</v>
-      </c>
+      <c r="S32" s="15" t="n"/>
       <c r="T32" s="15" t="n">
         <v>424</v>
       </c>
@@ -6205,12 +6231,8 @@
       <c r="R33" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="15" t="n">
-        <v>16823</v>
-      </c>
-      <c r="T33" s="15" t="n">
-        <v>1993</v>
-      </c>
+      <c r="S33" s="15" t="n"/>
+      <c r="T33" s="15" t="n"/>
       <c r="U33" s="15" t="n">
         <v>2732</v>
       </c>
@@ -6464,9 +6486,7 @@
       <c r="S35" s="15" t="n">
         <v>628</v>
       </c>
-      <c r="T35" s="15" t="n">
-        <v>1205</v>
-      </c>
+      <c r="T35" s="15" t="n"/>
       <c r="U35" s="15" t="n">
         <v>110000</v>
       </c>
@@ -6485,22 +6505,48 @@
       <c r="Z35" s="16" t="n">
         <v>0.00117</v>
       </c>
-      <c r="AA35" s="15" t="n"/>
+      <c r="AA35" s="15" t="n">
+        <v>27</v>
+      </c>
       <c r="AB35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="15" t="n"/>
-      <c r="AD35" s="14" t="n"/>
-      <c r="AE35" s="14" t="n"/>
-      <c r="AF35" s="14" t="n"/>
-      <c r="AG35" s="14" t="n"/>
-      <c r="AH35" s="14" t="n"/>
-      <c r="AI35" s="14" t="n"/>
-      <c r="AJ35" s="14" t="n"/>
-      <c r="AK35" s="14" t="n"/>
-      <c r="AL35" s="14" t="n"/>
-      <c r="AM35" s="14" t="n"/>
-      <c r="AN35" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE35" s="14" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AF35" s="14" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AG35" s="14" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="AH35" s="14" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI35" s="14" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AJ35" s="14" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="AK35" s="14" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AL35" s="14" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AM35" s="14" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="AN35" s="14" t="n">
+        <v>26.7</v>
+      </c>
       <c r="AO35" s="14" t="n"/>
       <c r="AP35" s="14" t="n"/>
       <c r="AQ35" s="14" t="n"/>
@@ -6952,9 +6998,7 @@
       <c r="S39" s="15" t="n">
         <v>820</v>
       </c>
-      <c r="T39" s="15" t="n">
-        <v>1083</v>
-      </c>
+      <c r="T39" s="15" t="n"/>
       <c r="U39" s="15" t="n">
         <v>8510</v>
       </c>
@@ -7060,9 +7104,7 @@
       <c r="S40" s="15" t="n">
         <v>566</v>
       </c>
-      <c r="T40" s="15" t="n">
-        <v>1744</v>
-      </c>
+      <c r="T40" s="15" t="n"/>
       <c r="U40" s="15" t="n">
         <v>23415</v>
       </c>
@@ -7165,9 +7207,7 @@
       <c r="R41" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="15" t="n">
-        <v>4310</v>
-      </c>
+      <c r="S41" s="15" t="n"/>
       <c r="T41" s="15" t="n">
         <v>251</v>
       </c>
@@ -7190,7 +7230,7 @@
         <v>0.0064</v>
       </c>
       <c r="AA41" s="15" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AB41" s="15" t="n">
         <v>1</v>
@@ -7200,19 +7240,19 @@
       </c>
       <c r="AD41" s="14" t="n"/>
       <c r="AE41" s="14" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AF41" s="14" t="n">
         <v>29</v>
       </c>
       <c r="AG41" s="14" t="n">
-        <v>18.18</v>
+        <v>17.9</v>
       </c>
       <c r="AH41" s="14" t="n">
-        <v>39.5</v>
+        <v>38</v>
       </c>
       <c r="AI41" s="14" t="n">
-        <v>53.5</v>
+        <v>52.72</v>
       </c>
       <c r="AJ41" s="14" t="n"/>
       <c r="AK41" s="14" t="n"/>
@@ -7227,7 +7267,7 @@
         <v>13</v>
       </c>
       <c r="AP41" s="14" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="AQ41" s="14" t="n"/>
       <c r="AR41" s="15" t="n">
@@ -7423,9 +7463,7 @@
       <c r="R43" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="15" t="n">
-        <v>1527</v>
-      </c>
+      <c r="S43" s="15" t="n"/>
       <c r="T43" s="15" t="n">
         <v>305</v>
       </c>
@@ -7444,7 +7482,7 @@
       </c>
       <c r="Z43" s="16" t="n"/>
       <c r="AA43" s="15" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AB43" s="15" t="n">
         <v>1</v>
@@ -7464,7 +7502,7 @@
       <c r="AK43" s="14" t="n"/>
       <c r="AL43" s="14" t="n"/>
       <c r="AM43" s="14" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AN43" s="14" t="n">
         <v>35</v>
@@ -7540,9 +7578,7 @@
       <c r="S44" s="15" t="n">
         <v>364</v>
       </c>
-      <c r="T44" s="15" t="n">
-        <v>1486</v>
-      </c>
+      <c r="T44" s="15" t="n"/>
       <c r="U44" s="15" t="n">
         <v>34668</v>
       </c>
@@ -7666,7 +7702,7 @@
         <v>0.00343</v>
       </c>
       <c r="AA45" s="15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AB45" s="15" t="n">
         <v>1</v>
@@ -7790,7 +7826,7 @@
         <v>0.00173</v>
       </c>
       <c r="AA46" s="15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB46" s="15" t="n">
         <v>1</v>
@@ -7806,13 +7842,13 @@
         <v>12</v>
       </c>
       <c r="AG46" s="14" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="AH46" s="14" t="n">
         <v>24</v>
       </c>
       <c r="AI46" s="14" t="n">
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="AJ46" s="14" t="n"/>
       <c r="AK46" s="14" t="n"/>
@@ -7890,9 +7926,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="15" t="n"/>
-      <c r="T47" s="15" t="n">
-        <v>1175</v>
-      </c>
+      <c r="T47" s="15" t="n"/>
       <c r="U47" s="15" t="n">
         <v>18698</v>
       </c>
@@ -7912,7 +7946,7 @@
         <v>0.00693</v>
       </c>
       <c r="AA47" s="15" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="AB47" s="15" t="n">
         <v>1</v>
@@ -7922,31 +7956,31 @@
       </c>
       <c r="AD47" s="14" t="n"/>
       <c r="AE47" s="14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AF47" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG47" s="14" t="n">
-        <v>43</v>
+        <v>41.75</v>
       </c>
       <c r="AH47" s="14" t="n">
-        <v>47.5</v>
+        <v>44</v>
       </c>
       <c r="AI47" s="14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AJ47" s="14" t="n"/>
       <c r="AK47" s="14" t="n"/>
       <c r="AL47" s="14" t="n"/>
       <c r="AM47" s="14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AN47" s="14" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AO47" s="14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP47" s="14" t="n">
         <v>8</v>
@@ -8018,9 +8052,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="15" t="n"/>
-      <c r="T48" s="15" t="n">
-        <v>1152</v>
-      </c>
+      <c r="T48" s="15" t="n"/>
       <c r="U48" s="15" t="n">
         <v>25555</v>
       </c>
@@ -8039,12 +8071,18 @@
       <c r="Z48" s="16" t="n">
         <v>0.01197</v>
       </c>
-      <c r="AA48" s="15" t="n"/>
+      <c r="AA48" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="AB48" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="15" t="n"/>
-      <c r="AD48" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC48" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" s="14" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AE48" s="14" t="n"/>
       <c r="AF48" s="14" t="n"/>
       <c r="AG48" s="14" t="n"/>
@@ -8458,7 +8496,7 @@
         <v>0.03043</v>
       </c>
       <c r="AA52" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB52" s="15" t="n">
         <v>1</v>
@@ -8481,7 +8519,7 @@
         <v>36</v>
       </c>
       <c r="AN52" s="14" t="n">
-        <v>54</v>
+        <v>44.5</v>
       </c>
       <c r="AO52" s="14" t="n"/>
       <c r="AP52" s="14" t="n"/>
@@ -8568,7 +8606,7 @@
       <c r="Y53" s="14" t="n"/>
       <c r="Z53" s="16" t="n"/>
       <c r="AA53" s="15" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AB53" s="15" t="n">
         <v>1</v>
@@ -8584,13 +8622,13 @@
         <v>25.9</v>
       </c>
       <c r="AG53" s="14" t="n">
-        <v>28.4</v>
+        <v>30.4</v>
       </c>
       <c r="AH53" s="14" t="n">
         <v>32.7</v>
       </c>
       <c r="AI53" s="14" t="n">
-        <v>37.6</v>
+        <v>43.6</v>
       </c>
       <c r="AJ53" s="14" t="n"/>
       <c r="AK53" s="14" t="n"/>
@@ -8670,9 +8708,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="15" t="n"/>
-      <c r="T54" s="15" t="n">
-        <v>1681</v>
-      </c>
+      <c r="T54" s="15" t="n"/>
       <c r="U54" s="15" t="n">
         <v>87929</v>
       </c>
@@ -8692,7 +8728,7 @@
         <v>0.0023</v>
       </c>
       <c r="AA54" s="15" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AB54" s="15" t="n">
         <v>1</v>
@@ -8705,16 +8741,16 @@
         <v>17.9</v>
       </c>
       <c r="AF54" s="14" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="AG54" s="14" t="n">
-        <v>34.9</v>
+        <v>35.55</v>
       </c>
       <c r="AH54" s="14" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="AI54" s="14" t="n">
-        <v>67.67</v>
+        <v>71.42</v>
       </c>
       <c r="AJ54" s="14" t="n"/>
       <c r="AK54" s="14" t="n"/>
@@ -8732,7 +8768,7 @@
         <v>6.75</v>
       </c>
       <c r="AQ54" s="14" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="AR54" s="15" t="n"/>
     </row>
@@ -8797,9 +8833,7 @@
       <c r="R55" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="15" t="n">
-        <v>1300</v>
-      </c>
+      <c r="S55" s="15" t="n"/>
       <c r="T55" s="15" t="n">
         <v>591</v>
       </c>
@@ -8822,7 +8856,7 @@
         <v>0.00084</v>
       </c>
       <c r="AA55" s="15" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB55" s="15" t="n">
         <v>1</v>
@@ -8838,13 +8872,13 @@
         <v>40</v>
       </c>
       <c r="AG55" s="14" t="n">
-        <v>52.75</v>
+        <v>55</v>
       </c>
       <c r="AH55" s="14" t="n">
         <v>65</v>
       </c>
       <c r="AI55" s="14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ55" s="14" t="n"/>
       <c r="AK55" s="14" t="n"/>
@@ -8856,7 +8890,7 @@
         <v>28</v>
       </c>
       <c r="AO55" s="14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP55" s="14" t="n">
         <v>8</v>
@@ -8927,9 +8961,7 @@
       <c r="R56" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="S56" s="19" t="n">
-        <v>15504</v>
-      </c>
+      <c r="S56" s="19" t="n"/>
       <c r="T56" s="19" t="n">
         <v>583</v>
       </c>

--- a/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
+++ b/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
@@ -3058,11 +3058,9 @@
         <v>1</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="14" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="14" t="n"/>
       <c r="AE7" s="14" t="n">
         <v>9</v>
       </c>
@@ -3070,7 +3068,7 @@
         <v>31</v>
       </c>
       <c r="AG7" s="14" t="n">
-        <v>34.5</v>
+        <v>34.75</v>
       </c>
       <c r="AH7" s="14" t="n">
         <v>40</v>
@@ -3078,15 +3076,9 @@
       <c r="AI7" s="14" t="n">
         <v>46.75</v>
       </c>
-      <c r="AJ7" s="14" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="AK7" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL7" s="14" t="n">
-        <v>76.75</v>
-      </c>
+      <c r="AJ7" s="14" t="n"/>
+      <c r="AK7" s="14" t="n"/>
+      <c r="AL7" s="14" t="n"/>
       <c r="AM7" s="14" t="n"/>
       <c r="AN7" s="14" t="n"/>
       <c r="AO7" s="14" t="n">
@@ -3638,15 +3630,17 @@
         <v>0.00249</v>
       </c>
       <c r="AA12" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AB12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="14" t="n"/>
       <c r="AE12" s="14" t="n">
         <v>12</v>
       </c>
@@ -3662,9 +3656,15 @@
       <c r="AI12" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="AJ12" s="14" t="n"/>
-      <c r="AK12" s="14" t="n"/>
-      <c r="AL12" s="14" t="n"/>
+      <c r="AJ12" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="AK12" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="AL12" s="14" t="n">
+        <v>62.5</v>
+      </c>
       <c r="AM12" s="14" t="n">
         <v>34</v>
       </c>
@@ -4032,15 +4032,17 @@
       </c>
       <c r="Z15" s="16" t="n"/>
       <c r="AA15" s="15" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AB15" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD15" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="AE15" s="14" t="n">
         <v>20</v>
       </c>
@@ -4056,9 +4058,15 @@
       <c r="AI15" s="14" t="n">
         <v>71.5</v>
       </c>
-      <c r="AJ15" s="14" t="n"/>
-      <c r="AK15" s="14" t="n"/>
-      <c r="AL15" s="14" t="n"/>
+      <c r="AJ15" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="AK15" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="AL15" s="14" t="n">
+        <v>94</v>
+      </c>
       <c r="AM15" s="14" t="n">
         <v>42</v>
       </c>
@@ -4906,15 +4914,17 @@
         <v>0.01027</v>
       </c>
       <c r="AA22" s="15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB22" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD22" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="AE22" s="14" t="n">
         <v>12</v>
       </c>
@@ -4930,9 +4940,15 @@
       <c r="AI22" s="14" t="n">
         <v>54.5</v>
       </c>
-      <c r="AJ22" s="14" t="n"/>
-      <c r="AK22" s="14" t="n"/>
-      <c r="AL22" s="14" t="n"/>
+      <c r="AJ22" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK22" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AL22" s="14" t="n">
+        <v>74.5</v>
+      </c>
       <c r="AM22" s="14" t="n">
         <v>38</v>
       </c>
@@ -5238,15 +5254,17 @@
       </c>
       <c r="Z25" s="16" t="n"/>
       <c r="AA25" s="15" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AB25" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD25" s="14" t="n">
+        <v>22.5</v>
+      </c>
       <c r="AE25" s="14" t="n">
         <v>25</v>
       </c>
@@ -5262,9 +5280,15 @@
       <c r="AI25" s="14" t="n">
         <v>75.75</v>
       </c>
-      <c r="AJ25" s="14" t="n"/>
-      <c r="AK25" s="14" t="n"/>
-      <c r="AL25" s="14" t="n"/>
+      <c r="AJ25" s="14" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="AK25" s="14" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AL25" s="14" t="n">
+        <v>99.5</v>
+      </c>
       <c r="AM25" s="14" t="n">
         <v>49</v>
       </c>
@@ -6124,15 +6148,17 @@
         <v>0.03412</v>
       </c>
       <c r="AA32" s="15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AB32" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD32" s="14" t="n">
+        <v>17.5</v>
+      </c>
       <c r="AE32" s="14" t="n">
         <v>18</v>
       </c>
@@ -6148,9 +6174,15 @@
       <c r="AI32" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="AJ32" s="14" t="n"/>
-      <c r="AK32" s="14" t="n"/>
-      <c r="AL32" s="14" t="n"/>
+      <c r="AJ32" s="14" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="AK32" s="14" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AL32" s="14" t="n">
+        <v>78.75</v>
+      </c>
       <c r="AM32" s="14" t="n">
         <v>29</v>
       </c>
@@ -6384,15 +6416,17 @@
         <v>0.00322</v>
       </c>
       <c r="AA34" s="15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB34" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD34" s="14" t="n">
+        <v>40</v>
+      </c>
       <c r="AE34" s="14" t="n">
         <v>27.9</v>
       </c>
@@ -6408,9 +6442,15 @@
       <c r="AI34" s="14" t="n">
         <v>76.8</v>
       </c>
-      <c r="AJ34" s="14" t="n"/>
-      <c r="AK34" s="14" t="n"/>
-      <c r="AL34" s="14" t="n"/>
+      <c r="AJ34" s="14" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="AK34" s="14" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AL34" s="14" t="n">
+        <v>118.05</v>
+      </c>
       <c r="AM34" s="14" t="n">
         <v>38</v>
       </c>
@@ -7230,15 +7270,17 @@
         <v>0.0064</v>
       </c>
       <c r="AA41" s="15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AB41" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC41" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD41" s="14" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AE41" s="14" t="n">
         <v>9</v>
       </c>
@@ -7254,9 +7296,15 @@
       <c r="AI41" s="14" t="n">
         <v>52.72</v>
       </c>
-      <c r="AJ41" s="14" t="n"/>
-      <c r="AK41" s="14" t="n"/>
-      <c r="AL41" s="14" t="n"/>
+      <c r="AJ41" s="14" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="AK41" s="14" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AL41" s="14" t="n">
+        <v>71.47</v>
+      </c>
       <c r="AM41" s="14" t="n">
         <v>38.9</v>
       </c>
@@ -7482,15 +7530,17 @@
       </c>
       <c r="Z43" s="16" t="n"/>
       <c r="AA43" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB43" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC43" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD43" s="14" t="n">
+        <v>28</v>
+      </c>
       <c r="AE43" s="14" t="n"/>
       <c r="AF43" s="14" t="n">
         <v>38</v>
@@ -7702,15 +7752,17 @@
         <v>0.00343</v>
       </c>
       <c r="AA45" s="15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB45" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC45" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD45" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="AE45" s="14" t="n">
         <v>12.5</v>
       </c>
@@ -7726,9 +7778,15 @@
       <c r="AI45" s="14" t="n">
         <v>30.25</v>
       </c>
-      <c r="AJ45" s="14" t="n"/>
-      <c r="AK45" s="14" t="n"/>
-      <c r="AL45" s="14" t="n"/>
+      <c r="AJ45" s="14" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AK45" s="14" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AL45" s="14" t="n">
+        <v>42.25</v>
+      </c>
       <c r="AM45" s="14" t="n"/>
       <c r="AN45" s="14" t="n">
         <v>18</v>
@@ -8978,15 +9036,17 @@
       </c>
       <c r="Z56" s="20" t="n"/>
       <c r="AA56" s="19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB56" s="19" t="n">
         <v>1</v>
       </c>
       <c r="AC56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="18" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD56" s="18" t="n">
+        <v>5</v>
+      </c>
       <c r="AE56" s="18" t="n">
         <v>7.5</v>
       </c>
@@ -9002,9 +9062,15 @@
       <c r="AI56" s="18" t="n">
         <v>81.5</v>
       </c>
-      <c r="AJ56" s="18" t="n"/>
-      <c r="AK56" s="18" t="n"/>
-      <c r="AL56" s="18" t="n"/>
+      <c r="AJ56" s="18" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="AK56" s="18" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AL56" s="18" t="n">
+        <v>86.5</v>
+      </c>
       <c r="AM56" s="18" t="n"/>
       <c r="AN56" s="18" t="n"/>
       <c r="AO56" s="18" t="n"/>

--- a/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
+++ b/dados/Dados agregados/B1_dados_agregados_resumido.xlsx
@@ -435,7 +435,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3183595"/>
+    <ext cx="5905500" cy="3176182"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -4532,7 +4532,7 @@
       <c r="Y19" s="14" t="n"/>
       <c r="Z19" s="16" t="n"/>
       <c r="AA19" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB19" s="15" t="n">
         <v>1</v>
@@ -4559,13 +4559,13 @@
         <v>75.8</v>
       </c>
       <c r="AJ19" s="14" t="n">
-        <v>88.05</v>
+        <v>86.8</v>
       </c>
       <c r="AK19" s="14" t="n">
         <v>95.8</v>
       </c>
       <c r="AL19" s="14" t="n">
-        <v>102.05</v>
+        <v>103.3</v>
       </c>
       <c r="AM19" s="14" t="n"/>
       <c r="AN19" s="14" t="n"/>
@@ -8004,15 +8004,17 @@
         <v>0.00693</v>
       </c>
       <c r="AA47" s="15" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AB47" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AC47" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="14" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD47" s="14" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AE47" s="14" t="n">
         <v>16</v>
       </c>
@@ -8028,9 +8030,15 @@
       <c r="AI47" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="AJ47" s="14" t="n"/>
-      <c r="AK47" s="14" t="n"/>
-      <c r="AL47" s="14" t="n"/>
+      <c r="AJ47" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="AK47" s="14" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AL47" s="14" t="n">
+        <v>70.75</v>
+      </c>
       <c r="AM47" s="14" t="n">
         <v>28</v>
       </c>
